--- a/exports/UNITDSPR_full_report.xlsx
+++ b/exports/UNITDSPR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.57</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>901</v>
+        <v>859.95</v>
       </c>
       <c r="I2" t="n">
         <v>900.2374348894441</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>1.05</v>
+        <v>-3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.63</v>
+        <v>3.99</v>
       </c>
       <c r="M2" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>5.49</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.68</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44616.55208333334</v>
+        <v>44617.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>849.9</v>
+        <v>883</v>
       </c>
       <c r="I3" t="n">
         <v>872.1369180541411</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>1.17</v>
+        <v>-2.68</v>
       </c>
       <c r="L3" t="n">
         <v>4.57</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.83</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44624.55208333334</v>
+        <v>44627.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>824.8</v>
+        <v>776.9</v>
       </c>
       <c r="I4" t="n">
         <v>824.2063397314876</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.59</v>
+        <v>-12.02</v>
       </c>
       <c r="L4" t="n">
-        <v>6.82</v>
+        <v>12.23</v>
       </c>
       <c r="M4" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="N4" t="n">
-        <v>5.47</v>
+        <v>6.52</v>
       </c>
       <c r="O4" t="n">
         <v>3.54</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>11.38</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="I5" t="n">
         <v>842.7501499067586</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.42</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>5.81</v>
+        <v>10.79</v>
       </c>
       <c r="M5" t="n">
-        <v>0.13</v>
+        <v>1.22</v>
       </c>
       <c r="N5" t="n">
         <v>3.67</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44649.38541666666</v>
+        <v>44649.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>868.35</v>
+        <v>860.8</v>
       </c>
       <c r="I6" t="n">
         <v>866.9992048139052</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>2.64</v>
+        <v>1.75</v>
       </c>
       <c r="L6" t="n">
         <v>2.33</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>5.65</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>900.3</v>
+        <v>910</v>
       </c>
       <c r="I7" t="n">
         <v>909.4146257206206</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.59</v>
+        <v>-5.72</v>
       </c>
       <c r="L7" t="n">
-        <v>5.11</v>
+        <v>6.57</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>4.8</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>892.8</v>
+        <v>887.85</v>
       </c>
       <c r="I8" t="n">
         <v>888.6839366302084</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.89</v>
+        <v>-2.43</v>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>3.99</v>
       </c>
       <c r="M8" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="N8" t="n">
         <v>2.27</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>5.16</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>778</v>
+        <v>821.2</v>
       </c>
       <c r="I9" t="n">
         <v>797.9549192226901</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>12.37</v>
+        <v>7.51</v>
       </c>
       <c r="L9" t="n">
         <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3.97</v>
+        <v>5.99</v>
       </c>
       <c r="O9" t="n">
         <v>-0.54</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>9.76</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44726.38541666666</v>
+        <v>44726.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>772.75</v>
+        <v>766.6</v>
       </c>
       <c r="I10" t="n">
         <v>769.7463302464273</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.9</v>
+        <v>-6.65</v>
       </c>
       <c r="L10" t="n">
-        <v>6.84</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
         <v>1.77</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>5.75</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44742.55208333334</v>
+        <v>44743.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>760.9</v>
+        <v>781.3</v>
       </c>
       <c r="I11" t="n">
         <v>780.36218636001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.74</v>
+        <v>-1.92</v>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>2.36</v>
       </c>
       <c r="M11" t="n">
         <v>1.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>3.44</v>
       </c>
       <c r="O11" t="n">
         <v>-1.83</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>7.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44768.55208333334</v>
+        <v>44769.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>848.75</v>
+        <v>788.05</v>
       </c>
       <c r="I12" t="n">
         <v>821.890574992986</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K12" t="n">
-        <v>8.630000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="L12" t="n">
         <v>3.49</v>
       </c>
       <c r="M12" t="n">
-        <v>0.53</v>
+        <v>1.62</v>
       </c>
       <c r="N12" t="n">
-        <v>1.83</v>
+        <v>6.86</v>
       </c>
       <c r="O12" t="n">
         <v>3.44</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.01</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44789.38541666666</v>
+        <v>44789.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>801.3</v>
+        <v>811.9</v>
       </c>
       <c r="I13" t="n">
         <v>809.759187448188</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.68</v>
+        <v>-3.03</v>
       </c>
       <c r="L13" t="n">
         <v>6.26</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>5.38</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>775</v>
+        <v>768.8</v>
       </c>
       <c r="I14" t="n">
         <v>771.1760577785674</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.54</v>
+        <v>-5.31</v>
       </c>
       <c r="L14" t="n">
-        <v>5.14</v>
+        <v>6.28</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
         <v>2.32</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>5.1</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44797.55208333334</v>
+        <v>44798.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>782</v>
+        <v>817.1</v>
       </c>
       <c r="I15" t="n">
         <v>805.6229288781004</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.72</v>
+        <v>-6.28</v>
       </c>
       <c r="L15" t="n">
-        <v>2.51</v>
+        <v>8.41</v>
       </c>
       <c r="M15" t="n">
         <v>1.19</v>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>4.16</v>
       </c>
       <c r="O15" t="n">
         <v>-0.79</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.69</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44845.38541666666</v>
+        <v>44845.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>827.5</v>
+        <v>809</v>
       </c>
       <c r="I16" t="n">
         <v>823.1104242966228</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K16" t="n">
-        <v>1.27</v>
+        <v>-0.99</v>
       </c>
       <c r="L16" t="n">
         <v>4.29</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>8.67</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44858.76041666666</v>
+        <v>44859.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>837</v>
+        <v>869.95</v>
       </c>
       <c r="I17" t="n">
         <v>858.2776631204578</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13.20833333333333</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.46</v>
+        <v>-7.53</v>
       </c>
       <c r="L17" t="n">
-        <v>4.45</v>
+        <v>7.73</v>
       </c>
       <c r="M17" t="n">
         <v>2.19</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>7.39</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44910.55208333334</v>
+        <v>44911.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>939.1</v>
+        <v>913.85</v>
       </c>
       <c r="I18" t="n">
         <v>913.8827226988964</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K18" t="n">
-        <v>7.95</v>
+        <v>5.05</v>
       </c>
       <c r="L18" t="n">
         <v>4.1</v>
       </c>
       <c r="M18" t="n">
-        <v>0.33</v>
+        <v>0.65</v>
       </c>
       <c r="N18" t="n">
-        <v>2.28</v>
+        <v>3.89</v>
       </c>
       <c r="O18" t="n">
         <v>3.05</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.2</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44999.38541666666</v>
+        <v>44999.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>763.35</v>
+        <v>768.8</v>
       </c>
       <c r="I19" t="n">
         <v>763.8003044191745</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>88</v>
+        <v>88.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>16.47</v>
+        <v>15.87</v>
       </c>
       <c r="L19" t="n">
         <v>2.81</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>3.92</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45012.38541666666</v>
+        <v>45012.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>752.8</v>
+        <v>746.95</v>
       </c>
       <c r="I20" t="n">
         <v>749.134745970793</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.08</v>
+        <v>-2.84</v>
       </c>
       <c r="L20" t="n">
-        <v>2.08</v>
+        <v>2.97</v>
       </c>
       <c r="M20" t="n">
         <v>2.21</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>5.11</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45033.55208333334</v>
+        <v>45034.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>765.6</v>
+        <v>779</v>
       </c>
       <c r="I21" t="n">
         <v>768.6063928258046</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.5</v>
+        <v>-4.29</v>
       </c>
       <c r="L21" t="n">
-        <v>3.03</v>
+        <v>5.11</v>
       </c>
       <c r="M21" t="n">
         <v>0.8</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.66</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45131.38541666666</v>
+        <v>45131.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>984.5</v>
+        <v>977.6</v>
       </c>
       <c r="I22" t="n">
         <v>979.0042223331876</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>97</v>
+        <v>97.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>26.38</v>
+        <v>25.49</v>
       </c>
       <c r="L22" t="n">
         <v>3.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>7.28</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45159.55208333334</v>
+        <v>45160.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1000.95</v>
+        <v>1034.55</v>
       </c>
       <c r="I23" t="n">
         <v>1018.269615395663</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.39</v>
+        <v>-5.83</v>
       </c>
       <c r="L23" t="n">
-        <v>5.36</v>
+        <v>6.03</v>
       </c>
       <c r="M23" t="n">
         <v>0.87</v>
       </c>
       <c r="N23" t="n">
-        <v>1.49</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>-5.82</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.96</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1039.75</v>
+        <v>1010.5</v>
       </c>
       <c r="I24" t="n">
         <v>1025.997660621157</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>-2.32</v>
       </c>
       <c r="L24" t="n">
         <v>3.61</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>6.6</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45205.38541666666</v>
+        <v>45205.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1018.7</v>
+        <v>1026.5</v>
       </c>
       <c r="I25" t="n">
         <v>1021.082071482871</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.58</v>
       </c>
       <c r="L25" t="n">
         <v>2.72</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.21</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1040</v>
+        <v>1018.3</v>
       </c>
       <c r="I26" t="n">
         <v>1039.426273670808</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>1.32</v>
+        <v>-0.8</v>
       </c>
       <c r="L26" t="n">
         <v>2</v>
@@ -1923,7 +2234,7 @@
         <v>1.33</v>
       </c>
       <c r="N26" t="n">
-        <v>2.58</v>
+        <v>2.98</v>
       </c>
       <c r="O26" t="n">
         <v>1.53</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>5.76</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45232.38541666666</v>
+        <v>45232.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="I27" t="n">
         <v>1053.743568501015</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.11</v>
+        <v>-4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>3.89</v>
+        <v>4.56</v>
       </c>
       <c r="M27" t="n">
         <v>1.37</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>4.54</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45239.55208333334</v>
+        <v>45240.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1097.2</v>
+        <v>1041.6</v>
       </c>
       <c r="I28" t="n">
         <v>1046.909271552478</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>3.51</v>
+        <v>-1.74</v>
       </c>
       <c r="L28" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="M28" t="n">
-        <v>0.06</v>
+        <v>1.57</v>
       </c>
       <c r="N28" t="n">
-        <v>0.21</v>
+        <v>4.63</v>
       </c>
       <c r="O28" t="n">
         <v>1.44</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.56</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45273.55208333334</v>
+        <v>45274.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1074</v>
+        <v>1083.95</v>
       </c>
       <c r="I29" t="n">
         <v>1076.569803597498</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.11</v>
+        <v>-4.07</v>
       </c>
       <c r="L29" t="n">
-        <v>3.83</v>
+        <v>4.55</v>
       </c>
       <c r="M29" t="n">
         <v>1.78</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>3.89</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45327.38541666666</v>
+        <v>45327.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1071.1</v>
+        <v>1061</v>
       </c>
       <c r="I30" t="n">
         <v>1065.172132150006</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.19</v>
+        <v>-2.12</v>
       </c>
       <c r="L30" t="n">
         <v>3.36</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.66</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45335.55208333334</v>
+        <v>45336.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1112.1</v>
+        <v>1128.2</v>
       </c>
       <c r="I31" t="n">
         <v>1119.292802589438</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.82</v>
+        <v>-6.33</v>
       </c>
       <c r="L31" t="n">
-        <v>5.52</v>
+        <v>6.59</v>
       </c>
       <c r="M31" t="n">
         <v>1.23</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>6.02</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1119.7</v>
+        <v>1105.65</v>
       </c>
       <c r="I32" t="n">
         <v>1115.55376730996</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.75</v>
+        <v>-2</v>
       </c>
       <c r="L32" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="M32" t="n">
         <v>0.6</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>5.86</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1133.15</v>
+        <v>1158.85</v>
       </c>
       <c r="I33" t="n">
         <v>1148.940566190078</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.49</v>
+        <v>-4.81</v>
       </c>
       <c r="L33" t="n">
-        <v>5.1</v>
+        <v>5.82</v>
       </c>
       <c r="M33" t="n">
         <v>0.66</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.33</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45401.38541666666</v>
+        <v>45401.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1125.6</v>
+        <v>1122.7</v>
       </c>
       <c r="I34" t="n">
         <v>1124.633843152858</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.87</v>
+        <v>-3.12</v>
       </c>
       <c r="L34" t="n">
         <v>4.12</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>5.19</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45406.38541666666</v>
+        <v>45406.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1173.1</v>
+        <v>1182.75</v>
       </c>
       <c r="I35" t="n">
         <v>1180.944115111046</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.49</v>
+        <v>-5.35</v>
       </c>
       <c r="L35" t="n">
-        <v>5.69</v>
+        <v>6.49</v>
       </c>
       <c r="M35" t="n">
         <v>0.28</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.92</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45439.38541666666</v>
+        <v>45439.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>1169.4</v>
+        <v>1151.9</v>
       </c>
       <c r="I36" t="n">
         <v>1156.919426297358</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.13</v>
+        <v>-2.61</v>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
         <v>0.72</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.47</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1210.05</v>
+        <v>1280.7</v>
       </c>
       <c r="I37" t="n">
         <v>1225.8409776983</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.05</v>
+        <v>-11.18</v>
       </c>
       <c r="L37" t="n">
-        <v>7.21</v>
+        <v>13.24</v>
       </c>
       <c r="M37" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="N37" t="n">
-        <v>2.94</v>
+        <v>6.69</v>
       </c>
       <c r="O37" t="n">
         <v>-2.37</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45457.55208333334</v>
+        <v>45461.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1270</v>
+        <v>1237.8</v>
       </c>
       <c r="I38" t="n">
         <v>1244.40945694258</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.84</v>
+        <v>-3.35</v>
       </c>
       <c r="L38" t="n">
         <v>5.34</v>
       </c>
       <c r="M38" t="n">
-        <v>0.19</v>
+        <v>0.39</v>
       </c>
       <c r="N38" t="n">
         <v>1.83</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.11</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45488.38541666666</v>
+        <v>45488.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1295</v>
+        <v>1305.3</v>
       </c>
       <c r="I39" t="n">
         <v>1304.331352238725</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.62</v>
+        <v>-5.45</v>
       </c>
       <c r="L39" t="n">
         <v>5.73</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.4</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1608.05</v>
+        <v>1550.1</v>
       </c>
       <c r="I40" t="n">
         <v>1555.129191818873</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>78</v>
+        <v>79.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>23.19</v>
+        <v>18.75</v>
       </c>
       <c r="L40" t="n">
         <v>3.2</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.46</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45614.55208333334</v>
+        <v>45615.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1469.55</v>
+        <v>1501.05</v>
       </c>
       <c r="I41" t="n">
         <v>1499.600902566003</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K41" t="n">
-        <v>5.2</v>
+        <v>3.16</v>
       </c>
       <c r="L41" t="n">
         <v>2.9</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.58</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1625</v>
+        <v>1579.6</v>
       </c>
       <c r="I42" t="n">
         <v>1606.383507356197</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K42" t="n">
-        <v>8.26</v>
+        <v>5.23</v>
       </c>
       <c r="L42" t="n">
         <v>2.28</v>
@@ -2835,7 +3338,7 @@
         <v>1.54</v>
       </c>
       <c r="N42" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="O42" t="n">
         <v>1.21</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.08</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45680.38541666666</v>
+        <v>45680.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="I43" t="n">
         <v>1497.359724129794</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K43" t="n">
-        <v>5.29</v>
+        <v>5.1</v>
       </c>
       <c r="L43" t="n">
         <v>3.25</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.54</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45684.55208333334</v>
+        <v>45685.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1403</v>
+        <v>1390.05</v>
       </c>
       <c r="I44" t="n">
         <v>1400.962485678725</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.4</v>
+        <v>-7.27</v>
       </c>
       <c r="L44" t="n">
-        <v>7.48</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>1.33</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45728.55208333334</v>
+        <v>45729.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1336.7</v>
+        <v>1359.55</v>
       </c>
       <c r="I45" t="n">
         <v>1354.849968797826</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K45" t="n">
-        <v>3.84</v>
+        <v>2.19</v>
       </c>
       <c r="L45" t="n">
         <v>8.550000000000001</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.49</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45805.55208333334</v>
+        <v>45806.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1527.6</v>
+        <v>1512.1</v>
       </c>
       <c r="I46" t="n">
         <v>1512.2249947321</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K46" t="n">
-        <v>12.36</v>
+        <v>11.22</v>
       </c>
       <c r="L46" t="n">
         <v>2.62</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>4.96</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45810.55208333334</v>
+        <v>45811.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1550</v>
+        <v>1586</v>
       </c>
       <c r="I47" t="n">
         <v>1585.490886490657</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.51</v>
+        <v>-4.89</v>
       </c>
       <c r="L47" t="n">
-        <v>2.59</v>
+        <v>6.46</v>
       </c>
       <c r="M47" t="n">
-        <v>0.01</v>
+        <v>1.87</v>
       </c>
       <c r="N47" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="O47" t="n">
         <v>-0.38</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.29</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45818.55208333334</v>
+        <v>45819.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1605</v>
+        <v>1501.4</v>
       </c>
       <c r="I48" t="n">
         <v>1536.64202858518</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>1.2</v>
+        <v>-5.33</v>
       </c>
       <c r="L48" t="n">
-        <v>1.54</v>
+        <v>6.52</v>
       </c>
       <c r="M48" t="n">
-        <v>-0</v>
+        <v>5.11</v>
       </c>
       <c r="N48" t="n">
-        <v>0.93</v>
+        <v>6.35</v>
       </c>
       <c r="O48" t="n">
         <v>1.8</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.4</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1327</v>
+        <v>1336</v>
       </c>
       <c r="I49" t="n">
         <v>1328.715770053038</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>83</v>
       </c>
       <c r="K49" t="n">
-        <v>11.62</v>
+        <v>11.02</v>
       </c>
       <c r="L49" t="n">
         <v>3.1</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>3.95</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45908.38541666666</v>
+        <v>45908.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1302.1</v>
+        <v>1295</v>
       </c>
       <c r="I50" t="n">
         <v>1297.547273348767</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.54</v>
+        <v>-3.07</v>
       </c>
       <c r="L50" t="n">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="M50" t="n">
         <v>0.38</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>3.92</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1331</v>
+        <v>1346.1</v>
       </c>
       <c r="I51" t="n">
         <v>1343.823651288832</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.78</v>
+        <v>-3.95</v>
       </c>
       <c r="L51" t="n">
-        <v>3.92</v>
+        <v>5.25</v>
       </c>
       <c r="M51" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="N51" t="n">
         <v>1.29</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>2.92</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1317.8</v>
+        <v>1301.7</v>
       </c>
       <c r="I52" t="n">
         <v>1309.163465563772</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.1</v>
+        <v>-3.3</v>
       </c>
       <c r="L52" t="n">
-        <v>2.33</v>
+        <v>3.39</v>
       </c>
       <c r="M52" t="n">
         <v>0.53</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.54</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45930.55208333334</v>
+        <v>45931.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1331.1</v>
+        <v>1348.7</v>
       </c>
       <c r="I53" t="n">
         <v>1348.330620243609</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.26</v>
+        <v>-3.61</v>
       </c>
       <c r="L53" t="n">
-        <v>3.1</v>
+        <v>4.08</v>
       </c>
       <c r="M53" t="n">
         <v>0.45</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>4.96</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45944.38541666666</v>
+        <v>45944.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1308</v>
+        <v>1302.6</v>
       </c>
       <c r="I54" t="n">
         <v>1306.765378212164</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.02</v>
+        <v>-3.42</v>
       </c>
       <c r="L54" t="n">
-        <v>3.02</v>
+        <v>3.61</v>
       </c>
       <c r="M54" t="n">
         <v>0.28</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>3.76</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1333</v>
+        <v>1356.3</v>
       </c>
       <c r="I55" t="n">
         <v>1351.605395431125</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.33</v>
+        <v>-4.12</v>
       </c>
       <c r="L55" t="n">
-        <v>2.49</v>
+        <v>4.15</v>
       </c>
       <c r="M55" t="n">
         <v>0.64</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.13</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46008.55208333334</v>
+        <v>46009.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1414.1</v>
+        <v>1397.6</v>
       </c>
       <c r="I56" t="n">
         <v>1406.501990460918</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K56" t="n">
-        <v>4.26</v>
+        <v>3.05</v>
       </c>
       <c r="L56" t="n">
         <v>2.3</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>3.58</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46052.38541666666</v>
+        <v>46052.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1352.6</v>
+        <v>1363</v>
       </c>
       <c r="I57" t="n">
         <v>1356.434599379891</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K57" t="n">
-        <v>3.22</v>
+        <v>2.48</v>
       </c>
       <c r="L57" t="n">
         <v>3.92</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>4.52</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1380.1</v>
+        <v>1361.5</v>
       </c>
       <c r="I58" t="n">
         <v>1378.513828914637</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>1.25</v>
+        <v>-0.11</v>
       </c>
       <c r="L58" t="n">
         <v>3.76</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.54</v>
       </c>
       <c r="N58" t="n">
         <v>1.89</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.49</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46086.55208333334</v>
+        <v>46087.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1328</v>
+        <v>1392.2</v>
       </c>
       <c r="I59" t="n">
         <v>1388.093908448505</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>2.46</v>
+        <v>-2.25</v>
       </c>
       <c r="L59" t="n">
-        <v>0.97</v>
+        <v>2.47</v>
       </c>
       <c r="M59" t="n">
         <v>0.01</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="O59" t="n">
         <v>-0.86</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.23</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1314.3</v>
+        <v>1310.4</v>
       </c>
       <c r="I60" t="n">
         <v>1311.726180650218</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>-5.6</v>
+        <v>-5.88</v>
       </c>
       <c r="L60" t="n">
-        <v>6.13</v>
+        <v>6.44</v>
       </c>
       <c r="M60" t="n">
         <v>0.9399999999999999</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.93</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46128.55208333334</v>
+        <v>46129.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1255</v>
+        <v>1300</v>
       </c>
       <c r="I61" t="n">
         <v>1294.759218654332</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K61" t="n">
-        <v>4.23</v>
+        <v>0.79</v>
       </c>
       <c r="L61" t="n">
         <v>4.04</v>
@@ -3918,7 +4649,7 @@
         <v>3.36</v>
       </c>
       <c r="N61" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="O61" t="n">
         <v>-0.2</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>7.01</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1366.9</v>
+        <v>1325.6</v>
       </c>
       <c r="I62" t="n">
         <v>1337.84541778931</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>5.15</v>
+        <v>1.97</v>
       </c>
       <c r="L62" t="n">
         <v>3.47</v>
       </c>
       <c r="M62" t="n">
-        <v>0.06</v>
+        <v>1.24</v>
       </c>
       <c r="N62" t="n">
-        <v>1.16</v>
+        <v>2.85</v>
       </c>
       <c r="O62" t="n">
         <v>3.95</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.73</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46156.55208333334</v>
+        <v>46157.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1271.7</v>
+        <v>1339.7</v>
       </c>
       <c r="I63" t="n">
         <v>1306.147339914307</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>4.07</v>
+        <v>-1.06</v>
       </c>
       <c r="L63" t="n">
         <v>1.84</v>
       </c>
       <c r="M63" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="N63" t="n">
-        <v>1.06</v>
+        <v>3.4</v>
       </c>
       <c r="O63" t="n">
         <v>-2.85</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.16</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1258</v>
+        <v>1253.2</v>
       </c>
       <c r="I64" t="n">
         <v>1255.130999254001</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.1</v>
+        <v>-6.46</v>
       </c>
       <c r="L64" t="n">
-        <v>6.28</v>
+        <v>7.06</v>
       </c>
       <c r="M64" t="n">
         <v>0.26</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>4.48</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46188.55208333334</v>
+        <v>46189.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1272</v>
+        <v>1295.8</v>
       </c>
       <c r="I65" t="n">
         <v>1288.446517925447</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.5</v>
+        <v>-3.4</v>
       </c>
       <c r="L65" t="n">
-        <v>2.86</v>
+        <v>3.46</v>
       </c>
       <c r="M65" t="n">
         <v>1.07</v>
       </c>
       <c r="N65" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="O65" t="n">
         <v>-1.49</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.17</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46218.38541666666</v>
+        <v>46218.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1379.8</v>
+        <v>1373</v>
       </c>
       <c r="I66" t="n">
         <v>1374.518009065117</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>6.48</v>
+        <v>5.96</v>
       </c>
       <c r="L66" t="n">
         <v>2.14</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>4.23</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46226.55208333334</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1415.9</v>
+        <v>1477.5</v>
       </c>
       <c r="I67" t="n">
         <v>1429.250815646596</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.12</v>
+        <v>-7.61</v>
       </c>
       <c r="L67" t="n">
-        <v>4.54</v>
+        <v>7.79</v>
       </c>
       <c r="M67" t="n">
         <v>0.21</v>
       </c>
       <c r="N67" t="n">
-        <v>1.46</v>
+        <v>3.4</v>
       </c>
       <c r="O67" t="n">
         <v>-1.14</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.46</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1500</v>
+        <v>1487</v>
       </c>
       <c r="I68" t="n">
         <v>1499.55917623126</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K68" t="n">
-        <v>1.52</v>
+        <v>0.64</v>
       </c>
       <c r="L68" t="n">
         <v>4.53</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>4.46</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1362.1</v>
+        <v>1388.9</v>
       </c>
       <c r="I69" t="n">
         <v>1381.96680609292</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K69" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="L69" t="n">
         <v>1.61</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>5.84</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1360.3</v>
+        <v>1305</v>
       </c>
       <c r="I70" t="n">
         <v>1325.900672176669</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.06</v>
+        <v>-6.04</v>
       </c>
       <c r="L70" t="n">
-        <v>2.22</v>
+        <v>7.68</v>
       </c>
       <c r="M70" t="n">
         <v>0.67</v>
       </c>
       <c r="N70" t="n">
-        <v>1.51</v>
+        <v>4.8</v>
       </c>
       <c r="O70" t="n">
         <v>2</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>10</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.5</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7510,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.75</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.42</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.38</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.68</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.25</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.550000000000001</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7650,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.33</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.54</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.82</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
